--- a/sensitivity_results/legacy/multiconcept/summary_iv3.xlsx
+++ b/sensitivity_results/legacy/multiconcept/summary_iv3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\Downloads\results\sensitivity_summmary\Updatedsummary\mnetsmall\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\ONEDRI~1\DOCUME~1\MobaXterm\slash\srikant1_soc5cg44242y1\RemoteFiles\4003332_2_13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773E35F4-624E-4296-A399-062928714A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108FF27E-6461-48C4-B93F-3F361E22AA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="iv3_Class_0_all" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
     <sheet name="Summary" sheetId="16" r:id="rId16"/>
     <sheet name="PValue" sheetId="17" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Summary!$A$1:$Z$97</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35425,6 +35428,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z97" xr:uid="{00000000-0001-0000-0F00-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
